--- a/data/trans_bre/P19C09-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C09-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 4,5</t>
+          <t>-2,1; 4,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 10,29</t>
+          <t>2,34; 10,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 4,31</t>
+          <t>-4,3; 3,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-70,14; 467,14</t>
+          <t>-69,27; 471,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 1874,73</t>
+          <t>21,66; 2228,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,89; 163,9</t>
+          <t>-63,91; 135,33</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,57</t>
+          <t>-2,85; 2,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,21</t>
+          <t>-0,81; 2,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,61</t>
+          <t>-3,69; 0,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,79; 141,66</t>
+          <t>-56,85; 125,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 692,19</t>
+          <t>-51,72; 529,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,26; 73,55</t>
+          <t>-88,46; 60,09</t>
         </is>
       </c>
     </row>
@@ -794,27 +794,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,78</t>
+          <t>-1,17; 4,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 4,15</t>
+          <t>-0,57; 3,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,74</t>
+          <t>-1,47; 2,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 642,03</t>
+          <t>-45,08; 718,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,01; 889,52</t>
+          <t>-40,01; 814,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 2,7</t>
+          <t>-3,73; 2,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,9</t>
+          <t>-2,73; 3,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 2,13</t>
+          <t>-5,07; 2,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,48; 188,79</t>
+          <t>-65,32; 165,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 223,88</t>
+          <t>-59,57; 216,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 54,23</t>
+          <t>-59,08; 49,53</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 2,98</t>
+          <t>-4,85; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 3,7</t>
+          <t>-2,73; 4,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 4,84</t>
+          <t>-4,65; 4,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-85,62; 215,15</t>
+          <t>-84,68; 216,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-77,61; 306,01</t>
+          <t>-74,47; 302,21</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,61</t>
+          <t>-2,61; 3,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,73</t>
+          <t>-0,86; 4,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,2</t>
+          <t>-0,84; 4,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-81,63; 491,53</t>
+          <t>-78,38; 554,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,47; 923,74</t>
+          <t>-46,29; 843,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,38</t>
+          <t>-0,06; 4,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,49</t>
+          <t>-2,0; 1,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,83</t>
+          <t>-1,55; 2,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 332,72</t>
+          <t>-6,5; 329,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-63,55; 115,9</t>
+          <t>-62,13; 105,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,49; 242,65</t>
+          <t>-49,76; 238,88</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,25</t>
+          <t>-2,04; 1,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,41</t>
+          <t>-1,08; 1,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,93</t>
+          <t>-1,97; 0,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 112,81</t>
+          <t>-71,55; 103,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-66,24; 419,95</t>
+          <t>-76,87; 536,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,8; 86,99</t>
+          <t>-71,06; 83,16</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,46</t>
+          <t>-0,34; 1,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,95</t>
+          <t>0,31; 1,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,66</t>
+          <t>-1,1; 0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 68,66</t>
+          <t>-11,74; 69,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,85; 142,09</t>
+          <t>13,82; 140,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 27,7</t>
+          <t>-33,27; 29,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C09-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C09-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,42</t>
+          <t>-2,07; 4,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 10,92</t>
+          <t>2,49; 10,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,88</t>
+          <t>-3,47; 4,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-69,27; 471,18</t>
+          <t>-67,78; 522,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,66; 2228,5</t>
+          <t>32,02; 2108,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,91; 135,33</t>
+          <t>-58,68; 144,29</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,52</t>
+          <t>-2,82; 2,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,99</t>
+          <t>-0,84; 3,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,49</t>
+          <t>-3,77; 0,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-56,85; 125,01</t>
+          <t>-59,04; 130,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,72; 529,73</t>
+          <t>-59,83; 515,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,46; 60,09</t>
+          <t>-87,28; 70,45</t>
         </is>
       </c>
     </row>
@@ -794,27 +794,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,54</t>
+          <t>-0,71; 4,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,82</t>
+          <t>-0,72; 3,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,38</t>
+          <t>-1,38; 2,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-45,08; 718,18</t>
+          <t>-41,13; 535,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 814,14</t>
+          <t>-44,63; 792,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 2,68</t>
+          <t>-3,65; 2,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,72</t>
+          <t>-2,73; 3,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 2,1</t>
+          <t>-5,14; 2,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,32; 165,83</t>
+          <t>-70,21; 151,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,57; 216,39</t>
+          <t>-57,44; 229,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,08; 49,53</t>
+          <t>-59,75; 46,95</t>
         </is>
       </c>
     </row>
@@ -954,22 +954,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 2,8</t>
+          <t>-4,59; 2,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 4,06</t>
+          <t>-2,97; 3,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 4,9</t>
+          <t>-4,28; 5,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-84,68; 216,06</t>
+          <t>-87,67; 181,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-74,47; 302,21</t>
+          <t>-71,48; 360,39</t>
         </is>
       </c>
     </row>
@@ -1034,27 +1034,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 3,68</t>
+          <t>-2,66; 3,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,76</t>
+          <t>-0,85; 5,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,1</t>
+          <t>-0,71; 3,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,38; 554,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,29; 843,1</t>
+          <t>-60,78; 829,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,52</t>
+          <t>-0,17; 4,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,49</t>
+          <t>-1,91; 1,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,75</t>
+          <t>-1,46; 2,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 329,76</t>
+          <t>-9,68; 326,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-62,13; 105,11</t>
+          <t>-56,85; 111,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-49,76; 238,88</t>
+          <t>-49,14; 247,45</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,3</t>
+          <t>-2,06; 1,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,49</t>
+          <t>-0,88; 1,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,95</t>
+          <t>-1,94; 1,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-71,55; 103,57</t>
+          <t>-68,02; 107,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,87; 536,85</t>
+          <t>-71,5; 491,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,06; 83,16</t>
+          <t>-71,75; 84,01</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,45</t>
+          <t>-0,35; 1,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,93</t>
+          <t>0,27; 1,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,7</t>
+          <t>-1,05; 0,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 69,72</t>
+          <t>-11,64; 66,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,82; 140,94</t>
+          <t>12,43; 136,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 29,64</t>
+          <t>-32,54; 30,67</t>
         </is>
       </c>
     </row>
